--- a/utils/monday_sprint_sprint_2025-4.xlsx
+++ b/utils/monday_sprint_sprint_2025-4.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="174">
   <si>
     <t>Ticket</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
   </si>
   <si>
     <t>A fazer</t>
@@ -1480,21 +1483,21 @@
         <v>53</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
@@ -1506,10 +1509,10 @@
         <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>19</v>
@@ -1538,7 +1541,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
@@ -1550,10 +1553,10 @@
         <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>32</v>
@@ -1582,7 +1585,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -1594,10 +1597,10 @@
         <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>19</v>
@@ -1626,7 +1629,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
@@ -1638,10 +1641,10 @@
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>19</v>
@@ -1670,7 +1673,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -1682,10 +1685,10 @@
         <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>19</v>
@@ -1703,7 +1706,7 @@
         <v>17</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>21</v>
@@ -1714,7 +1717,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -1726,10 +1729,10 @@
         <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>19</v>
@@ -1747,7 +1750,7 @@
         <v>17</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>21</v>
@@ -1758,7 +1761,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -1770,10 +1773,10 @@
         <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>19</v>
@@ -1802,7 +1805,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -1814,10 +1817,10 @@
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
@@ -1846,7 +1849,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -1858,10 +1861,10 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -1879,7 +1882,7 @@
         <v>17</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>21</v>
@@ -1902,10 +1905,10 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -1946,10 +1949,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -1990,10 +1993,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
@@ -2034,10 +2037,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
@@ -2078,10 +2081,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2122,10 +2125,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>19</v>
@@ -2166,10 +2169,10 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>19</v>
@@ -2210,10 +2213,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2231,7 +2234,7 @@
         <v>17</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>21</v>
@@ -2254,10 +2257,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>19</v>
@@ -2275,7 +2278,7 @@
         <v>17</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>21</v>
@@ -2298,10 +2301,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2319,7 +2322,7 @@
         <v>17</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>21</v>
@@ -2330,22 +2333,22 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>19</v>
@@ -2374,22 +2377,22 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>19</v>
@@ -2418,7 +2421,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2430,10 +2433,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
@@ -2462,7 +2465,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2474,10 +2477,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
@@ -2506,7 +2509,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -2518,10 +2521,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2550,7 +2553,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -2562,10 +2565,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>19</v>
@@ -2594,7 +2597,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -2606,10 +2609,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
@@ -2638,7 +2641,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2650,10 +2653,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>19</v>
@@ -2682,7 +2685,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -2694,10 +2697,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>32</v>
@@ -2726,7 +2729,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -2738,10 +2741,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>19</v>
@@ -2770,7 +2773,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -2782,10 +2785,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -2814,7 +2817,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -2826,10 +2829,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>19</v>
@@ -2858,7 +2861,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -2870,10 +2873,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -2902,7 +2905,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -2914,10 +2917,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>19</v>
@@ -2946,7 +2949,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -2958,10 +2961,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -2990,7 +2993,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3002,10 +3005,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3034,7 +3037,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3046,10 +3049,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3078,7 +3081,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3090,10 +3093,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3122,7 +3125,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3134,10 +3137,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
@@ -3166,7 +3169,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3178,10 +3181,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3210,7 +3213,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3222,10 +3225,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
@@ -3254,7 +3257,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3266,10 +3269,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
@@ -3298,7 +3301,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3310,10 +3313,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>19</v>
@@ -3342,7 +3345,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3354,10 +3357,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3386,7 +3389,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3398,10 +3401,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3430,7 +3433,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3442,10 +3445,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3474,7 +3477,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3486,10 +3489,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3518,7 +3521,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3530,10 +3533,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -3606,7 +3609,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3618,10 +3621,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
@@ -3650,7 +3653,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3662,10 +3665,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -3694,7 +3697,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -3706,10 +3709,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -3749,23 +3752,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3773,16 +3776,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3801,7 +3804,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3822,7 +3825,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3853,12 +3856,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B2">
         <v>62</v>
@@ -3882,25 +3885,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3917,13 +3920,13 @@
         <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3955,13 +3958,13 @@
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K11">
         <v>62</v>
       </c>
       <c r="M11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -3995,7 +3998,7 @@
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -4007,7 +4010,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -4015,7 +4018,7 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -4029,7 +4032,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4037,7 +4040,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4045,7 +4048,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4053,7 +4056,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -4064,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4078,7 +4081,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>49</v>

--- a/utils/monday_sprint_sprint_2025-4.xlsx
+++ b/utils/monday_sprint_sprint_2025-4.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="207">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>29930</t>
+    <t>8438679960</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,13 +87,10 @@
     <t>09/02/2025</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Impedimento</t>
   </si>
   <si>
-    <t>Aberto</t>
+    <t>Não</t>
   </si>
   <si>
     <t>Semana 2</t>
@@ -102,7 +99,7 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>29680</t>
+    <t>8455587125</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -117,19 +114,22 @@
     <t>11/02/2025</t>
   </si>
   <si>
+    <t>19/02/2025</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>29677</t>
+    <t>8455595221</t>
   </si>
   <si>
     <t>Qlik Sense - Base do WMS e Etiqueta Amarela (Entrada e estoque)</t>
   </si>
   <si>
-    <t>27180 / 30029</t>
+    <t>18/02/2025</t>
+  </si>
+  <si>
+    <t>8441453755</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -144,28 +144,34 @@
     <t>10/02/2025</t>
   </si>
   <si>
-    <t>29812</t>
+    <t>20/02/2025</t>
+  </si>
+  <si>
+    <t>8438534629</t>
   </si>
   <si>
     <t>CONSULTA DE FTF NO GED</t>
   </si>
   <si>
-    <t>29499</t>
+    <t>8441361782</t>
   </si>
   <si>
     <t>Tempo padrão - CPP x CRP Atualização Automática</t>
   </si>
   <si>
-    <t>29254</t>
+    <t>8454487482</t>
   </si>
   <si>
     <t>Layout do relatório do PDI</t>
   </si>
   <si>
+    <t>23/02/2025</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
-    <t>29922</t>
+    <t>8475752429</t>
   </si>
   <si>
     <t>Criar campo para controle de refugo prodtivo</t>
@@ -174,13 +180,16 @@
     <t>13/02/2025</t>
   </si>
   <si>
-    <t>28956</t>
+    <t>8442628620</t>
   </si>
   <si>
     <t>PDI_RespostaNew – A sequência que apresentar laudo ‘Analisar’ ou ‘Retrabalho’ criar nova PDI.</t>
   </si>
   <si>
-    <t>29476</t>
+    <t>12/02/2025</t>
+  </si>
+  <si>
+    <t>8327524229</t>
   </si>
   <si>
     <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
@@ -198,6 +207,9 @@
     <t>29853</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -219,88 +231,124 @@
     <t>A fazer</t>
   </si>
   <si>
-    <t>29678</t>
+    <t>8441995440</t>
   </si>
   <si>
     <t>Qlik Sense - Base do Recibo de Embarque e Tickets</t>
   </si>
   <si>
-    <t>29599</t>
+    <t>8441996043</t>
   </si>
   <si>
     <t>Relatório de Contas a receber - Gerencial no SENSE</t>
   </si>
   <si>
-    <t>29788</t>
+    <t>8438489214</t>
   </si>
   <si>
     <t>CARACTERES CAMPO DE OBSERVAÇÃO - DESMOLDAGEM</t>
   </si>
   <si>
-    <t>29477</t>
+    <t>8441996480</t>
   </si>
   <si>
     <t>Qlik Sense - Custos de Exportação "ID"</t>
   </si>
   <si>
-    <t>29897</t>
+    <t>8438678773</t>
   </si>
   <si>
     <t>Formulário 596</t>
   </si>
   <si>
-    <t>29478</t>
+    <t>8441996363</t>
   </si>
   <si>
     <t>Qlik Sense - Custos de Venda Geral</t>
   </si>
   <si>
+    <t>22/02/2025</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>8327456143</t>
+  </si>
+  <si>
+    <t>8441997029</t>
   </si>
   <si>
     <t>Atualização das parcelas programadas - Reunião</t>
   </si>
   <si>
-    <t>29314</t>
+    <t>8441262050</t>
   </si>
   <si>
     <t>Erro sistema PCP Usinagem ( Erro de comunicação)</t>
   </si>
   <si>
+    <t>8454452750</t>
+  </si>
+  <si>
     <t>Ajustar título (descrição das telas)</t>
   </si>
   <si>
+    <t>8454455796</t>
+  </si>
+  <si>
     <t>Tela de login usar masterpage sem menu</t>
   </si>
   <si>
+    <t>8454458237</t>
+  </si>
+  <si>
     <t>Usar Ícones diferentes por item do menu</t>
   </si>
   <si>
+    <t>8454462086</t>
+  </si>
+  <si>
     <t>No cadastro de cotas adicionar coluna com informação de STATUS (fechada/iniciada)</t>
   </si>
   <si>
+    <t>8454466567</t>
+  </si>
+  <si>
     <t>Verificar na tela PDI_RespostaNew a mensagem "undefined" para cada registro</t>
   </si>
   <si>
+    <t>8454470440</t>
+  </si>
+  <si>
     <t>retirar as mensagem multiplas</t>
   </si>
   <si>
+    <t>8454479626</t>
+  </si>
+  <si>
     <t>Testar importação da planilha e consistir para não ficar "travado"</t>
   </si>
   <si>
+    <t>8454482976</t>
+  </si>
+  <si>
     <t>Movimentar sequencia para pendencia de qualidade (setor: 5534) quando PDI_RespostaNew.status = "Analisar/avaliar" (atividade depende da publicação do Web service)</t>
   </si>
   <si>
+    <t>8454491880</t>
+  </si>
+  <si>
     <t>Montar relatório de pendências (filtro por status)</t>
   </si>
   <si>
+    <t>8454496671</t>
+  </si>
+  <si>
     <t>Envio automático de alerta para avaliação do analista</t>
   </si>
   <si>
-    <t>29686</t>
+    <t>8455411118</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -309,49 +357,55 @@
     <t>•	Desenvolver rotina de escrita na tabela APON3 e APON31</t>
   </si>
   <si>
+    <t>8455417694</t>
+  </si>
+  <si>
     <t>•	Integração de Inserção, Atualização e Exclusão de apontamentos e paradas com a apon3</t>
   </si>
   <si>
-    <t>29256</t>
+    <t>16/02/2025</t>
+  </si>
+  <si>
+    <t>8462542840</t>
   </si>
   <si>
     <t>Permitir informar manualmente o sequencial no cadastro de cotas.</t>
   </si>
   <si>
-    <t>12/02/2025</t>
-  </si>
-  <si>
-    <t>29844</t>
+    <t>8438587686</t>
   </si>
   <si>
     <t>Valor do ICMS Diferido - XML</t>
   </si>
   <si>
-    <t>29863</t>
+    <t>8438600887</t>
   </si>
   <si>
     <t>Remover coluna</t>
   </si>
   <si>
-    <t>29679</t>
+    <t>8441995279</t>
   </si>
   <si>
     <t>Valor de Venda EXW + Custo de Entrega</t>
   </si>
   <si>
-    <t>29869</t>
+    <t>8438603502</t>
   </si>
   <si>
     <t>Imprimir endereço</t>
   </si>
   <si>
-    <t>29538</t>
+    <t>8441996253</t>
   </si>
   <si>
     <t>Proforma GIBELA 1530/24</t>
   </si>
   <si>
-    <t>29132</t>
+    <t>17/02/2025</t>
+  </si>
+  <si>
+    <t>8232353355</t>
   </si>
   <si>
     <t>Melhorias sistema Ronda</t>
@@ -360,43 +414,43 @@
     <t>13/01/2025</t>
   </si>
   <si>
-    <t>29784</t>
+    <t>8438481193</t>
   </si>
   <si>
     <t>Melhoria Relatório PCP Estorno de Refugos</t>
   </si>
   <si>
-    <t>29778</t>
+    <t>8438463217</t>
   </si>
   <si>
     <t>Aviso por E-mail</t>
   </si>
   <si>
-    <t>29746</t>
+    <t>8438461391</t>
   </si>
   <si>
     <t>Botão de visualização do centro de custo</t>
   </si>
   <si>
-    <t>29792</t>
+    <t>8438491697</t>
   </si>
   <si>
     <t>TRAVA ID - SISTEMA INVOICES</t>
   </si>
   <si>
-    <t>29870</t>
+    <t>8438610380</t>
   </si>
   <si>
     <t>Apontamentos Inspeção JAN/2025</t>
   </si>
   <si>
-    <t>29798</t>
+    <t>8438514477</t>
   </si>
   <si>
     <t>Regra para Planilhão na Etapa Moldagem</t>
   </si>
   <si>
-    <t>29107</t>
+    <t>8337371877</t>
   </si>
   <si>
     <t>MPO Esmerilhadeiras e Retíficas - Ajustagem</t>
@@ -405,91 +459,94 @@
     <t>27/01/2025</t>
   </si>
   <si>
-    <t>28847</t>
+    <t>8441996862</t>
   </si>
   <si>
     <t>Habilitar o sistema de apontamento dos manipuladores para o acabamento</t>
   </si>
   <si>
-    <t>29816</t>
+    <t>8438548145</t>
   </si>
   <si>
     <t>Manter registro na tela atual</t>
   </si>
   <si>
-    <t>29959</t>
+    <t>8438685103</t>
   </si>
   <si>
     <t>Conferência consignados - Três pontos</t>
   </si>
   <si>
-    <t>29933</t>
+    <t>8438682439</t>
   </si>
   <si>
     <t>ERRO Apontamento de Horas - ACABAMENTO (Revisão Ticket 23310)</t>
   </si>
   <si>
-    <t>29972</t>
+    <t>8438687043</t>
   </si>
   <si>
     <t>Sistema ERP || DIFA CTEs</t>
   </si>
   <si>
-    <t>29815</t>
+    <t>8438539752</t>
   </si>
   <si>
     <t>NÚMERO DE MODELO TELA DE MOVIMENTAÇÃO PCP</t>
   </si>
   <si>
-    <t>29840</t>
+    <t>8438581782</t>
   </si>
   <si>
     <t>PRÉ-EMBARQUE NAC Sequencia</t>
   </si>
   <si>
-    <t>29888</t>
+    <t>8438616236</t>
   </si>
   <si>
     <t>Hora parada - Sistema de corridas</t>
   </si>
   <si>
-    <t>29942</t>
+    <t>8438683143</t>
   </si>
   <si>
     <t>PERDCOMP REINTEGRA SISTEMA INVOICE</t>
   </si>
   <si>
-    <t>29823</t>
+    <t>8438567858</t>
   </si>
   <si>
     <t>Colunas no arquivo do MPS</t>
   </si>
   <si>
-    <t>29977</t>
+    <t>8438689467</t>
   </si>
   <si>
     <t>Solicitação de Ajuste Automático nos Campos de Frete e Seguro na OTF</t>
   </si>
   <si>
-    <t>29932</t>
+    <t>8438681236</t>
   </si>
   <si>
     <t>ERRO: Apontamento de Horas - ACABAMENTO Deltractor</t>
   </si>
   <si>
-    <t>29822</t>
+    <t>8441995879</t>
+  </si>
+  <si>
+    <t>8438560967</t>
   </si>
   <si>
     <t>Alteração preço itens consignados</t>
   </si>
   <si>
-    <t>29825</t>
+    <t>8438575319</t>
   </si>
   <si>
     <t>Indicadores GIQ</t>
   </si>
   <si>
-    <t>28957</t>
+    <t>8441951711</t>
   </si>
   <si>
     <t>Controle estoque manutenção usinagem</t>
@@ -501,7 +558,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-4</t>
+    <t>Jan/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -553,6 +610,9 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1087,113 +1147,113 @@
         <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -1228,39 +1288,39 @@
         <v>42</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1275,39 +1335,39 @@
         <v>23</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1322,39 +1382,39 @@
         <v>42</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1366,42 +1426,42 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>41</v>
@@ -1413,42 +1473,42 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1463,39 +1523,39 @@
         <v>42</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1507,89 +1567,89 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1604,39 +1664,39 @@
         <v>42</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>41</v>
@@ -1651,39 +1711,39 @@
         <v>42</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1698,39 +1758,39 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1745,39 +1805,39 @@
         <v>42</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1792,39 +1852,39 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1839,39 +1899,39 @@
         <v>42</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1883,27 +1943,27 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1915,10 +1975,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1933,39 +1993,39 @@
         <v>42</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1980,39 +2040,39 @@
         <v>42</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2024,42 +2084,42 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2071,42 +2131,42 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2118,42 +2178,42 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2165,42 +2225,42 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2212,42 +2272,42 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2259,42 +2319,42 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2306,42 +2366,42 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2353,42 +2413,42 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2400,42 +2460,42 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2447,42 +2507,42 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2494,42 +2554,42 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2541,42 +2601,42 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2588,42 +2648,42 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2638,39 +2698,39 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2685,39 +2745,39 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2732,39 +2792,39 @@
         <v>42</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2779,39 +2839,39 @@
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2826,39 +2886,39 @@
         <v>42</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>41</v>
@@ -2870,42 +2930,42 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2920,39 +2980,39 @@
         <v>23</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2967,39 +3027,39 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3014,39 +3074,39 @@
         <v>23</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3061,39 +3121,39 @@
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3108,39 +3168,39 @@
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3155,39 +3215,39 @@
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3199,27 +3259,27 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3231,10 +3291,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3249,39 +3309,39 @@
         <v>42</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3296,39 +3356,39 @@
         <v>23</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3343,24 +3403,24 @@
         <v>23</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3372,10 +3432,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3390,39 +3450,39 @@
         <v>23</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3437,39 +3497,39 @@
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3484,39 +3544,39 @@
         <v>23</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3531,39 +3591,39 @@
         <v>23</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3578,39 +3638,39 @@
         <v>23</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3625,39 +3685,39 @@
         <v>23</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3672,39 +3732,39 @@
         <v>23</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>34</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3719,24 +3779,24 @@
         <v>23</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3748,10 +3808,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3766,39 +3826,39 @@
         <v>23</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="F60" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -3813,39 +3873,39 @@
         <v>42</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -3860,39 +3920,39 @@
         <v>23</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -3907,39 +3967,39 @@
         <v>23</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -3954,19 +4014,19 @@
         <v>42</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3982,23 +4042,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4006,16 +4066,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4026,20 +4086,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K22">
         <v>40</v>
@@ -4055,7 +4115,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4086,12 +4146,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B2">
         <v>62</v>
@@ -4105,35 +4165,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4141,40 +4201,46 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10">
         <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N10">
         <v>40</v>
       </c>
       <c r="P10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q10">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
@@ -4188,25 +4254,25 @@
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K11">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="M11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N11">
         <v>6</v>
       </c>
       <c r="P11" t="s">
-        <v>58</v>
+        <v>199</v>
       </c>
       <c r="Q11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="4:14" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
         <v>39</v>
       </c>
@@ -4220,33 +4286,39 @@
         <v>57</v>
       </c>
       <c r="J12" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
+      <c r="P12" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q12">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -4254,7 +4326,7 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -4268,7 +4340,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4276,7 +4348,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4284,7 +4356,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4292,10 +4364,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -4303,7 +4375,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4311,142 +4383,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
